--- a/Dokumen/Physical Design (Database).xlsx
+++ b/Dokumen/Physical Design (Database).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 7\KP\Point-Of-Sale-App\Dokumen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DFEED8-D484-4194-B0AE-3518662047C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2358857C-045F-4E1F-B7EE-E92A6E25E19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="2595" windowWidth="15375" windowHeight="7875" xr2:uid="{3829DD94-4D69-4851-A80E-D00989EEAB47}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{3829DD94-4D69-4851-A80E-D00989EEAB47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="220">
   <si>
     <t>Tabel role_user</t>
   </si>
@@ -610,6 +610,90 @@
   </si>
   <si>
     <t>Bertindak sebagai Cabang Asal/Default kasir tersebut ditugaskan.</t>
+  </si>
+  <si>
+    <t>Tabel shift_operator_logs</t>
+  </si>
+  <si>
+    <t>id_log</t>
+  </si>
+  <si>
+    <t>aksi</t>
+  </si>
+  <si>
+    <t>waktu_kejadian</t>
+  </si>
+  <si>
+    <t>catatan</t>
+  </si>
+  <si>
+    <t>ENUM('open','break','resume','switch','closed')</t>
+  </si>
+  <si>
+    <t>Merujuk ke id_shift di tabel shift_session. (ON DELETE CASCADE).</t>
+  </si>
+  <si>
+    <t>Merujuk ke id_user kasir/operator pemicu aksi di tabel user.</t>
+  </si>
+  <si>
+    <t>Jenis aktivitas/status shift yang dicatat.</t>
+  </si>
+  <si>
+    <t>Waktu presisi ketika aksi dilakukan.</t>
+  </si>
+  <si>
+    <t>Keterangan/catatan tambahan aksi log.</t>
+  </si>
+  <si>
+    <t>Tabel audit_logs</t>
+  </si>
+  <si>
+    <t>id_audit</t>
+  </si>
+  <si>
+    <t>aktivitas</t>
+  </si>
+  <si>
+    <t>tabel_target</t>
+  </si>
+  <si>
+    <t>id_target</t>
+  </si>
+  <si>
+    <t>data_sebelum</t>
+  </si>
+  <si>
+    <t>data_sesudah</t>
+  </si>
+  <si>
+    <t>ip_address</t>
+  </si>
+  <si>
+    <t>VARCHAR(45)</t>
+  </si>
+  <si>
+    <t>Merujuk ke id_user yang melakukan modifikasi data di tabel user.</t>
+  </si>
+  <si>
+    <t>Jenis aktivitas modifikasi (misal: 'create_promo', 'update_price').</t>
+  </si>
+  <si>
+    <t>Nama tabel database target yang dimodifikasi.</t>
+  </si>
+  <si>
+    <t>ID unik baris data pada tabel target yang dimodifikasi.</t>
+  </si>
+  <si>
+    <t>Nilai record data sebelum dimodifikasi untuk jejak audit.</t>
+  </si>
+  <si>
+    <t>Nilai record data baru setelah dimodifikasi.</t>
+  </si>
+  <si>
+    <t>Waktu presisi kejadian modifikasi data.</t>
+  </si>
+  <si>
+    <t>Alamat IP dari klien/admin pengubah data.</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A44815-6356-4CDA-BB15-A8CF31194A7C}">
-  <dimension ref="B2:F128"/>
+  <dimension ref="B2:F149"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2838,6 +2922,305 @@
         <v>179</v>
       </c>
     </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B130" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B131" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B132" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B133" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B134" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B135" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B136" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B137" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B139" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B140" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B141" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B142" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B143" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B144" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B145" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B146" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B147" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B148" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B149" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Dokumen/Physical Design (Database).xlsx
+++ b/Dokumen/Physical Design (Database).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 7\KP\Point-Of-Sale-App\Dokumen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2358857C-045F-4E1F-B7EE-E92A6E25E19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A8E83D-4E7E-43CE-B5CB-3EE6F976687C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{3829DD94-4D69-4851-A80E-D00989EEAB47}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" xr2:uid="{3829DD94-4D69-4851-A80E-D00989EEAB47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="223">
   <si>
     <t>Tabel role_user</t>
   </si>
@@ -694,6 +694,15 @@
   </si>
   <si>
     <t>Alamat IP dari klien/admin pengubah data.</t>
+  </si>
+  <si>
+    <t>deleted_at</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Menyimpan waktu penghapusan logis (soft delete) untuk data cabang.</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A44815-6356-4CDA-BB15-A8CF31194A7C}">
-  <dimension ref="B2:F149"/>
+  <dimension ref="B2:F154"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1277,65 +1286,65 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+    <row r="13" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+    <row r="17" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
@@ -1344,348 +1353,370 @@
         <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+    <row r="20" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="D20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+    <row r="21" spans="2:6" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+    <row r="22" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+    <row r="23" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+    <row r="24" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+    <row r="28" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="E28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
+    <row r="29" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="5" t="s">
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+    <row r="30" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
+    <row r="34" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="E34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+    <row r="35" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="C35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
+    <row r="36" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="D36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
+    <row r="37" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
+    <row r="41" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="E41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
+    <row r="42" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="E42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+    <row r="43" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="D43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>61</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="3" t="s">
-        <v>62</v>
+      <c r="B46" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
@@ -1707,7 +1738,7 @@
     </row>
     <row r="48" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
@@ -1719,211 +1750,182 @@
         <v>9</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
+    <row r="54" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="C54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="E54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="50" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
+    <row r="55" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="C55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="E55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
+    <row r="56" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="C56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="2" t="s">
+      <c r="E56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B52" s="5" t="s">
+    <row r="57" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" s="5" t="s">
+      <c r="D57" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
+    <row r="61" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="C61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="E61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>10</v>
@@ -1932,229 +1934,229 @@
         <v>26</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="2" t="s">
+      <c r="C71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="2" t="s">
+      <c r="E71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B67" s="2" t="s">
+    <row r="72" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" s="2" t="s">
+      <c r="D72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
+    <row r="73" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B73" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="2" t="s">
+      <c r="D73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="69" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B69" s="2" t="s">
+    <row r="74" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+      <c r="B74" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="2" t="s">
+      <c r="D74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F74" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B71" s="1" t="s">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B72" s="2" t="s">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B77" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B73" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B74" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B75" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B76" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B77" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="78" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B79" s="2" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>10</v>
@@ -2163,168 +2165,168 @@
         <v>26</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B81" s="2" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B85" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>176</v>
+        <v>9</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="87" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="89" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B89" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>68</v>
@@ -2333,866 +2335,866 @@
         <v>14</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B91" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B91" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B92" s="2" t="s">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>106</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B98" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B99" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D94" s="2" t="s">
+      <c r="C99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" s="2" t="s">
+      <c r="E99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="95" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B95" s="2" t="s">
+    <row r="100" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B100" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="2" t="s">
+      <c r="C100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" s="2" t="s">
+      <c r="E100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="96" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B96" s="2" t="s">
+    <row r="101" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B101" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" s="2" t="s">
+      <c r="D101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="97" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B97" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="98" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B98" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="99" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B99" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B100" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B101" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="102" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B102" s="2" t="s">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B103" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F102" s="2" t="s">
-        <v>171</v>
+      <c r="F103" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="104" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B104" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B104" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B105" s="2" t="s">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B106" s="2" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
     </row>
     <row r="107" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B107" s="2" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B108" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B109" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B109" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110" s="2" t="s">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B111" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B112" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B113" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B114" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B115" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B116" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E111" s="2" t="s">
+      <c r="D116" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F111" s="2" t="s">
+      <c r="F116" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="112" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B112" s="2" t="s">
+    <row r="117" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B117" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E112" s="2" t="s">
+      <c r="D117" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F112" s="2" t="s">
+      <c r="F117" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="113" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B113" s="2" t="s">
+    <row r="118" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B118" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F113" s="2" t="s">
+      <c r="D118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B114" s="5" t="s">
+    <row r="119" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B119" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C119" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D114" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E114" s="5" t="s">
+      <c r="D119" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F119" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B116" s="1" t="s">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B121" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B117" s="2" t="s">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B122" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D122" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="2" t="s">
+      <c r="F122" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B118" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B119" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B120" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B121" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B122" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="123" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B123" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+      <c r="B124" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+      <c r="B125" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B126" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B127" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B128" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" s="2" t="s">
+      <c r="D128" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="124" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B124" s="2" t="s">
+    <row r="129" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B129" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C129" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E124" s="2" t="s">
+      <c r="D129" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="F129" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="125" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B125" s="2" t="s">
+    <row r="130" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B130" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F125" s="2" t="s">
+      <c r="D130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="126" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B126" s="2" t="s">
+    <row r="131" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B131" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E126" s="2" t="s">
+      <c r="D131" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F126" s="2" t="s">
+      <c r="F131" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B127" s="2" t="s">
+    <row r="132" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+      <c r="B132" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E127" s="2" t="s">
+      <c r="D132" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F127" s="2" t="s">
+      <c r="F132" s="2" t="s">
         <v>174</v>
-      </c>
-    </row>
-    <row r="128" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B128" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B130" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B131" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B132" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="133" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B133" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B135" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B136" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B137" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B138" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D133" s="2" t="s">
+      <c r="C138" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F133" s="2" t="s">
+      <c r="E138" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="134" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B134" s="2" t="s">
+    <row r="139" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B139" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D134" s="2" t="s">
+      <c r="C139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134" s="2" t="s">
+      <c r="E139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="135" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B135" s="2" t="s">
+    <row r="140" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B140" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C140" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F135" s="2" t="s">
+      <c r="D140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="136" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B136" s="2" t="s">
+    <row r="141" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B141" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F136" s="2" t="s">
+      <c r="D141" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="137" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B137" s="2" t="s">
+    <row r="142" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B142" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E137" s="2" t="s">
+      <c r="D142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F137" s="2" t="s">
+      <c r="F142" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B139" s="1" t="s">
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B144" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B140" s="2" t="s">
+    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B145" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C145" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D145" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="E145" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="F145" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="141" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B141" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="142" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B142" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="143" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B143" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B144" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B145" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B146" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B147" s="2" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B148" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>14</v>
@@ -3201,23 +3203,108 @@
         <v>9</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="149" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B149" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B150" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B151" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B152" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B153" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B154" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E149" s="2" t="s">
+      <c r="D154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F149" s="2" t="s">
+      <c r="F154" s="2" t="s">
         <v>219</v>
       </c>
     </row>

--- a/Dokumen/Physical Design (Database).xlsx
+++ b/Dokumen/Physical Design (Database).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 7\KP\Point-Of-Sale-App\Dokumen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A8E83D-4E7E-43CE-B5CB-3EE6F976687C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEC8261-98D8-423C-B4A7-F42481E8C2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" xr2:uid="{3829DD94-4D69-4851-A80E-D00989EEAB47}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11385" xr2:uid="{3829DD94-4D69-4851-A80E-D00989EEAB47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="214">
   <si>
     <t>Tabel role_user</t>
   </si>
@@ -384,72 +384,15 @@
     <t>Total potongan diskon yang didapatkan.</t>
   </si>
   <si>
-    <t>ID unik internal untuk log pembayaran non-tunai berupa UUID v4.</t>
-  </si>
-  <si>
-    <t>ID transaksi unik resmi yang dikeluarkan oleh Midtrans/Xendit.</t>
-  </si>
-  <si>
-    <t>reference_number</t>
-  </si>
-  <si>
-    <t>payment_gateway_id</t>
-  </si>
-  <si>
-    <t>id_detail_bayar</t>
-  </si>
-  <si>
     <t>id_transaksi_detail</t>
   </si>
   <si>
-    <t>Nomor referensi bank / RRN (Retrieval Reference Number).</t>
-  </si>
-  <si>
-    <t>qr_string_data</t>
-  </si>
-  <si>
-    <t>Data teks mentah QRIS dari vendor untuk di-render jadi QR di APK.</t>
-  </si>
-  <si>
-    <t>va_number</t>
-  </si>
-  <si>
-    <t>Nomor Virtual Account (jika pelanggan memilih opsi bayar transfer bank).</t>
-  </si>
-  <si>
-    <t>status_api</t>
-  </si>
-  <si>
-    <t>ENUM('PENDING','SETTLEMENT','EXPIRED','DENIED')</t>
-  </si>
-  <si>
-    <t>DEFAULT 'PENDING'</t>
-  </si>
-  <si>
-    <t>Status pembayaran langsung dari server payment gateway.</t>
-  </si>
-  <si>
-    <t>waktu_kedaluwarsa</t>
-  </si>
-  <si>
     <t>DATETIME</t>
   </si>
   <si>
-    <t>Batas waktu akhir pelanggan harus membayar sebelum QRIS kedaluwarsa.</t>
-  </si>
-  <si>
-    <t>raw_callback_payload</t>
-  </si>
-  <si>
-    <t>Log mentah JSON Webhook untuk kebutuhan audit log finansial.</t>
-  </si>
-  <si>
     <t>id_sub_kategori</t>
   </si>
   <si>
-    <t>Tabel detail_pembayaran_non_tunai</t>
-  </si>
-  <si>
     <t>nama_sub_kategori</t>
   </si>
   <si>
@@ -513,12 +456,6 @@
     <t>kategori_metode</t>
   </si>
   <si>
-    <t>Pengelompokan metode (contoh: 'Tunai', 'QRIS', 'VA').</t>
-  </si>
-  <si>
-    <t>vendor_gateway</t>
-  </si>
-  <si>
     <t>Merujuk ke id_shift di tabel shift_session.</t>
   </si>
   <si>
@@ -552,18 +489,12 @@
     <t>Alasan spesifik mengapa item menu ini di-void.</t>
   </si>
   <si>
-    <t>Pihak ke-3 penyedia (contoh: 'Midtrans', 'Xendit', 'Direct'). Wajib diisi jika non-tunai dan wajib kosong jika tunai/cash.</t>
-  </si>
-  <si>
     <t>ENUM('OPEN', 'ON_BREAK','CLOSED')</t>
   </si>
   <si>
     <t>Menunjukkan status operasional shift kasir ('OPEN' = aktif, 'ON_BREAK' = jeda istirahat, 'CLOSED' = ditutup).</t>
   </si>
   <si>
-    <t>ENUM('Draft', 'Pending', 'Success', 'Void', 'Cancelled')</t>
-  </si>
-  <si>
     <t>DEFAULT 'Draft'</t>
   </si>
   <si>
@@ -576,9 +507,6 @@
     <t>Mencatat hasil selisih antara uang sistem dan uang fisik asli saat closing shift.</t>
   </si>
   <si>
-    <t>diperbaharui_oleh</t>
-  </si>
-  <si>
     <t>Merujuk ke id_user (Admin) yang melakukan koreksi manual atas transaksi ini.</t>
   </si>
   <si>
@@ -627,9 +555,6 @@
     <t>catatan</t>
   </si>
   <si>
-    <t>ENUM('open','break','resume','switch','closed')</t>
-  </si>
-  <si>
     <t>Merujuk ke id_shift di tabel shift_session. (ON DELETE CASCADE).</t>
   </si>
   <si>
@@ -703,13 +628,61 @@
   </si>
   <si>
     <t>Menyimpan waktu penghapusan logis (soft delete) untuk data cabang.</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Email resmi admin untuk pemulihan kata sandi.</t>
+  </si>
+  <si>
+    <t>Pengelompokan metode (contoh: 'Tunai', 'QRIS', 'VA', 'Transfer).</t>
+  </si>
+  <si>
+    <t>ENUM('Draft', 'Success', 'Void', 'Cancelled')</t>
+  </si>
+  <si>
+    <t>nomor_referensi</t>
+  </si>
+  <si>
+    <t>Untuk mencatat nomor RRN EDC / Bukti Transfer Non-Tunai Manual.</t>
+  </si>
+  <si>
+    <t>ENUM('open','break','resume','switch','closed', 'auto_closed')</t>
+  </si>
+  <si>
+    <t>Tabel password_reset_tokens</t>
+  </si>
+  <si>
+    <t>PK,FK</t>
+  </si>
+  <si>
+    <t>Merujuk ke email di tabel user.</t>
+  </si>
+  <si>
+    <t>token</t>
+  </si>
+  <si>
+    <t>Hash token reset password.</t>
+  </si>
+  <si>
+    <t>Waktu pembuatan token.</t>
+  </si>
+  <si>
+    <t>NULLABLE, UNIQUE</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>diperbarui_oleh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -722,6 +695,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -794,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -812,6 +791,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1128,13 +1110,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A44815-6356-4CDA-BB15-A8CF31194A7C}">
-  <dimension ref="B2:F154"/>
+  <dimension ref="B2:F149"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="25.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="1"/>
@@ -1237,10 +1219,10 @@
     </row>
     <row r="10" spans="2:6" ht="110.25" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -1249,7 +1231,7 @@
         <v>114</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -1288,10 +1270,10 @@
     </row>
     <row r="13" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -1300,7 +1282,7 @@
         <v>33</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
@@ -1373,7 +1355,7 @@
         <v>33</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="126" x14ac:dyDescent="0.25">
@@ -1427,408 +1409,408 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>40</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>220</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>221</v>
+        <v>38</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+      <c r="F25" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
+    <row r="29" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
+    <row r="30" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="5" t="s">
+      <c r="D30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="2" t="s">
+    <row r="31" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
+      <c r="F31" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2" t="s">
+    <row r="35" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="C36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="E36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>220</v>
+        <v>119</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>221</v>
+        <v>19</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
+      <c r="F38" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
+    <row r="42" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="E42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="2" t="s">
+    <row r="43" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="D44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="2" t="s">
+    <row r="45" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
+      <c r="F45" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
+    <row r="49" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="E49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
+    <row r="50" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="D50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B51" s="3" t="s">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
@@ -1840,12 +1822,12 @@
         <v>9</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
@@ -1857,233 +1839,233 @@
         <v>9</v>
       </c>
       <c r="F56" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B57" s="5" t="s">
+    <row r="58" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="5" t="s">
+      <c r="D58" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-    </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
+    <row r="62" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="2" t="s">
+      <c r="E62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="63" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="2" t="s">
+      <c r="D65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
+    <row r="66" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="D66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F67" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B68" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B69" s="1" t="s">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F71" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B71" s="2" t="s">
+    <row r="72" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" s="2" t="s">
+      <c r="C72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="E72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B72" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="73" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>13</v>
@@ -2095,12 +2077,12 @@
         <v>9</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>13</v>
@@ -2109,10 +2091,10 @@
         <v>14</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
@@ -2224,7 +2206,7 @@
     </row>
     <row r="83" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>10</v>
@@ -2236,7 +2218,7 @@
         <v>9</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -2341,26 +2323,26 @@
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B90" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="91" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B91" s="2" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>22</v>
@@ -2372,12 +2354,12 @@
         <v>33</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B92" s="2" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>10</v>
@@ -2389,12 +2371,12 @@
         <v>33</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="93" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>22</v>
@@ -2406,7 +2388,7 @@
         <v>33</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -2423,68 +2405,68 @@
         <v>114</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B96" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="B95" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B97" s="2" t="s">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B98" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E98" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="F98" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B98" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" s="2" t="s">
+    <row r="99" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B99" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="E99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="99" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B99" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="100" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B100" s="2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>10</v>
@@ -2496,403 +2478,403 @@
         <v>9</v>
       </c>
       <c r="F100" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B101" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B101" s="2" t="s">
+    <row r="102" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B102" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="2" t="s">
+      <c r="D102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="102" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B102" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="103" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B103" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B104" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="2" t="s">
+      <c r="C104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="F104" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="104" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B104" s="5" t="s">
+    <row r="105" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B105" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C105" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E104" s="5" t="s">
+      <c r="D105" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F105" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="105" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B105" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C105" s="2" t="s">
+    <row r="106" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B106" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="106" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B106" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D106" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>168</v>
+        <v>9</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B107" s="2" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C107" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B108" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E107" s="2" t="s">
+      <c r="D108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B109" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="F108" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B111" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D111" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E111" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="F111" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B111" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" s="2" t="s">
+    <row r="112" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B112" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B112" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="2" t="s">
+      <c r="E112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+      <c r="B113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="113" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B113" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E113" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="114" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6" ht="126" x14ac:dyDescent="0.25">
       <c r="B114" s="2" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="115" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B115" s="2" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="116" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B116" s="2" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="117" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B117" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="118" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B118" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C118" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" s="2" t="s">
+    </row>
+    <row r="119" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B119" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="119" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B119" s="5" t="s">
+      <c r="C119" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C119" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" s="5" t="s">
+    </row>
+    <row r="120" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F119" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B121" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F120" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" ht="126" x14ac:dyDescent="0.25">
+      <c r="B121" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B122" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B125" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B123" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D123" s="2" t="s">
+    <row r="126" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B126" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B124" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="125" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B125" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="126" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B126" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="E126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="127" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B127" s="2" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>10</v>
@@ -2904,49 +2886,49 @@
         <v>9</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="128" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B128" s="2" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="129" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B129" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="130" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B130" s="2" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>14</v>
@@ -2955,15 +2937,15 @@
         <v>9</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="131" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B131" s="2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>14</v>
@@ -2972,343 +2954,259 @@
         <v>33</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="132" spans="2:6" ht="126" x14ac:dyDescent="0.25">
-      <c r="B132" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="133" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B133" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B133" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F133" s="2" t="s">
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B134" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="B135" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B135" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C135" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B136" s="2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>5</v>
+        <v>187</v>
       </c>
     </row>
     <row r="137" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B137" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="138" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B138" s="2" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="139" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B139" s="2" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="140" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6" ht="63" x14ac:dyDescent="0.25">
       <c r="B140" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="141" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B141" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
     </row>
     <row r="142" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B142" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B143" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B145" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B146" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B147" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B148" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B149" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="D149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F142" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B144" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B145" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B146" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B147" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B148" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B149" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="F149" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B150" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="B151" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B152" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="153" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B153" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="154" spans="2:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B154" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>219</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
